--- a/10. Equity/work/fundamentals_model/20260715_ファンダメンタルズの検討②/outputs/history/scenario_quintile_return_history.xlsx
+++ b/10. Equity/work/fundamentals_model/20260715_ファンダメンタルズの検討②/outputs/history/scenario_quintile_return_history.xlsx
@@ -16528,7 +16528,7 @@
         <v>1</v>
       </c>
       <c r="F692" s="5">
-        <v>0.002991123082016141</v>
+        <v>0.003811878850881144</v>
       </c>
       <c r="G692" s="6">
         <v>14</v>
@@ -16551,7 +16551,7 @@
         <v>2</v>
       </c>
       <c r="F693" s="5">
-        <v>0.002385993529226867</v>
+        <v>0.002207446324060623</v>
       </c>
       <c r="G693" s="6">
         <v>14</v>
@@ -16574,7 +16574,7 @@
         <v>3</v>
       </c>
       <c r="F694" s="5">
-        <v>-0.01792265543711212</v>
+        <v>-0.02736014732650578</v>
       </c>
       <c r="G694" s="6">
         <v>15</v>
@@ -16597,7 +16597,7 @@
         <v>4</v>
       </c>
       <c r="F695" s="5">
-        <v>-0.01274138287375478</v>
+        <v>-0.006239554261991604</v>
       </c>
       <c r="G695" s="6">
         <v>14</v>
@@ -16620,7 +16620,7 @@
         <v>5</v>
       </c>
       <c r="F696" s="5">
-        <v>-0.002232619267499699</v>
+        <v>0.0005371045914628231</v>
       </c>
       <c r="G696" s="6">
         <v>15</v>
@@ -16643,7 +16643,7 @@
         <v>1</v>
       </c>
       <c r="F697" s="5">
-        <v>-0.01119439354122361</v>
+        <v>-0.004232721758588063</v>
       </c>
       <c r="G697" s="6">
         <v>14</v>
@@ -16666,7 +16666,7 @@
         <v>2</v>
       </c>
       <c r="F698" s="5">
-        <v>-0.009472129199186437</v>
+        <v>-0.00162627001396336</v>
       </c>
       <c r="G698" s="6">
         <v>14</v>
@@ -16689,7 +16689,7 @@
         <v>3</v>
       </c>
       <c r="F699" s="5">
-        <v>0.03013467397978553</v>
+        <v>0.01001179307041283</v>
       </c>
       <c r="G699" s="6">
         <v>15</v>
@@ -16712,7 +16712,7 @@
         <v>4</v>
       </c>
       <c r="F700" s="5">
-        <v>0.0045623755088621</v>
+        <v>0.01000355428605841</v>
       </c>
       <c r="G700" s="6">
         <v>14</v>
@@ -16735,7 +16735,7 @@
         <v>5</v>
       </c>
       <c r="F701" s="5">
-        <v>0.01179476617453081</v>
+        <v>0.01301885132185224</v>
       </c>
       <c r="G701" s="6">
         <v>15</v>
@@ -16758,7 +16758,7 @@
         <v>1</v>
       </c>
       <c r="F702" s="5">
-        <v>0.003996374474777148</v>
+        <v>0.002615845127437425</v>
       </c>
       <c r="G702" s="6">
         <v>14</v>
@@ -16781,7 +16781,7 @@
         <v>2</v>
       </c>
       <c r="F703" s="5">
-        <v>0.002571064296585805</v>
+        <v>-0.01666777000091201</v>
       </c>
       <c r="G703" s="6">
         <v>14</v>
@@ -16804,7 +16804,7 @@
         <v>3</v>
       </c>
       <c r="F704" s="5">
-        <v>-0.007175971554261678</v>
+        <v>-0.0162891212423455</v>
       </c>
       <c r="G704" s="6">
         <v>15</v>
@@ -16827,7 +16827,7 @@
         <v>4</v>
       </c>
       <c r="F705" s="5">
-        <v>0.0001620612561086135</v>
+        <v>0.006271546197384514</v>
       </c>
       <c r="G705" s="6">
         <v>14</v>
@@ -16850,7 +16850,7 @@
         <v>5</v>
       </c>
       <c r="F706" s="5">
-        <v>-0.006490809772561651</v>
+        <v>0.0161648933721797</v>
       </c>
       <c r="G706" s="6">
         <v>15</v>
@@ -16873,7 +16873,7 @@
         <v>1</v>
       </c>
       <c r="F707" s="5">
-        <v>0.00427041990943908</v>
+        <v>0.01169928455943325</v>
       </c>
       <c r="G707" s="6">
         <v>14</v>
@@ -16896,7 +16896,7 @@
         <v>2</v>
       </c>
       <c r="F708" s="5">
-        <v>0.02377719105484128</v>
+        <v>0.00946042326314612</v>
       </c>
       <c r="G708" s="6">
         <v>14</v>
@@ -16919,7 +16919,7 @@
         <v>3</v>
       </c>
       <c r="F709" s="5">
-        <v>0.02267797685285309</v>
+        <v>0.02929380458224733</v>
       </c>
       <c r="G709" s="6">
         <v>15</v>
@@ -16942,7 +16942,7 @@
         <v>4</v>
       </c>
       <c r="F710" s="5">
-        <v>0.02437927669929094</v>
+        <v>0.02722911943627146</v>
       </c>
       <c r="G710" s="6">
         <v>14</v>
@@ -16965,7 +16965,7 @@
         <v>5</v>
       </c>
       <c r="F711" s="5">
-        <v>0.01199458382461762</v>
+        <v>0.009147612472962495</v>
       </c>
       <c r="G711" s="6">
         <v>15</v>
@@ -16988,7 +16988,7 @@
         <v>1</v>
       </c>
       <c r="F712" s="5">
-        <v>0.002683035576536446</v>
+        <v>-0.00884597974769675</v>
       </c>
       <c r="G712" s="6">
         <v>14</v>
@@ -17011,7 +17011,7 @@
         <v>2</v>
       </c>
       <c r="F713" s="5">
-        <v>-0.01252676531903691</v>
+        <v>-0.01225877185587887</v>
       </c>
       <c r="G713" s="6">
         <v>14</v>
@@ -17034,7 +17034,7 @@
         <v>3</v>
       </c>
       <c r="F714" s="5">
-        <v>-0.01186782536242061</v>
+        <v>0.0078202576214613</v>
       </c>
       <c r="G714" s="6">
         <v>15</v>
@@ -17057,7 +17057,7 @@
         <v>4</v>
       </c>
       <c r="F715" s="5">
-        <v>-0.01437164954523747</v>
+        <v>-0.01338693755403584</v>
       </c>
       <c r="G715" s="6">
         <v>14</v>
@@ -17080,7 +17080,7 @@
         <v>5</v>
       </c>
       <c r="F716" s="5">
-        <v>-0.006728047154883523</v>
+        <v>-0.01682490759355014</v>
       </c>
       <c r="G716" s="6">
         <v>15</v>
@@ -17103,7 +17103,7 @@
         <v>1</v>
       </c>
       <c r="F717" s="5">
-        <v>0.0008316931451827393</v>
+        <v>-0.005458064301539156</v>
       </c>
       <c r="G717" s="6">
         <v>14</v>
@@ -17126,7 +17126,7 @@
         <v>2</v>
       </c>
       <c r="F718" s="5">
-        <v>0.01754283288194184</v>
+        <v>0.02824037475519689</v>
       </c>
       <c r="G718" s="6">
         <v>14</v>
@@ -17149,7 +17149,7 @@
         <v>3</v>
       </c>
       <c r="F719" s="5">
-        <v>0.008219627979699424</v>
+        <v>0.02299780875200807</v>
       </c>
       <c r="G719" s="6">
         <v>15</v>
@@ -17172,7 +17172,7 @@
         <v>4</v>
       </c>
       <c r="F720" s="5">
-        <v>0.01733608999020666</v>
+        <v>0.01520354594505832</v>
       </c>
       <c r="G720" s="6">
         <v>14</v>
@@ -17195,7 +17195,7 @@
         <v>5</v>
       </c>
       <c r="F721" s="5">
-        <v>0.01499422348053903</v>
+        <v>-0.001907514981062112</v>
       </c>
       <c r="G721" s="6">
         <v>15</v>
@@ -17218,7 +17218,7 @@
         <v>1</v>
       </c>
       <c r="F722" s="5">
-        <v>0.01111436055335762</v>
+        <v>0.007678595362733998</v>
       </c>
       <c r="G722" s="6">
         <v>14</v>
@@ -17241,7 +17241,7 @@
         <v>2</v>
       </c>
       <c r="F723" s="5">
-        <v>-0.01348400466799234</v>
+        <v>-0.0009977339986360129</v>
       </c>
       <c r="G723" s="6">
         <v>14</v>
@@ -17264,7 +17264,7 @@
         <v>3</v>
       </c>
       <c r="F724" s="5">
-        <v>0.01930840210539367</v>
+        <v>-3.64619534102333E-05</v>
       </c>
       <c r="G724" s="6">
         <v>15</v>
@@ -17287,7 +17287,7 @@
         <v>4</v>
       </c>
       <c r="F725" s="5">
-        <v>0.01706633740534474</v>
+        <v>0.02846467649232349</v>
       </c>
       <c r="G725" s="6">
         <v>14</v>
@@ -17310,7 +17310,7 @@
         <v>5</v>
       </c>
       <c r="F726" s="5">
-        <v>-0.004978030280254389</v>
+        <v>-0.004718754482781184</v>
       </c>
       <c r="G726" s="6">
         <v>15</v>
@@ -17333,7 +17333,7 @@
         <v>1</v>
       </c>
       <c r="F727" s="5">
-        <v>0.02846582460793331</v>
+        <v>0.03638192249160061</v>
       </c>
       <c r="G727" s="6">
         <v>14</v>
@@ -17356,7 +17356,7 @@
         <v>2</v>
       </c>
       <c r="F728" s="5">
-        <v>0.04025114583263908</v>
+        <v>0.01461283789472608</v>
       </c>
       <c r="G728" s="6">
         <v>14</v>
@@ -17379,7 +17379,7 @@
         <v>3</v>
       </c>
       <c r="F729" s="5">
-        <v>0.0154012837347673</v>
+        <v>0.03796267161923812</v>
       </c>
       <c r="G729" s="6">
         <v>15</v>
@@ -17402,7 +17402,7 @@
         <v>4</v>
       </c>
       <c r="F730" s="5">
-        <v>0.05588862628851487</v>
+        <v>0.037483387252525</v>
       </c>
       <c r="G730" s="6">
         <v>14</v>
@@ -17425,7 +17425,7 @@
         <v>5</v>
       </c>
       <c r="F731" s="5">
-        <v>0.02188463300062084</v>
+        <v>0.03304219760036988</v>
       </c>
       <c r="G731" s="6">
         <v>15</v>
@@ -17448,7 +17448,7 @@
         <v>1</v>
       </c>
       <c r="F732" s="5">
-        <v>0.04466980102314441</v>
+        <v>0.04394849778622721</v>
       </c>
       <c r="G732" s="6">
         <v>14</v>
@@ -17471,7 +17471,7 @@
         <v>2</v>
       </c>
       <c r="F733" s="5">
-        <v>0.02471302691157143</v>
+        <v>0.02993047345445535</v>
       </c>
       <c r="G733" s="6">
         <v>14</v>
@@ -17494,7 +17494,7 @@
         <v>3</v>
       </c>
       <c r="F734" s="5">
-        <v>0.0515545696326883</v>
+        <v>0.0508898431161606</v>
       </c>
       <c r="G734" s="6">
         <v>15</v>
@@ -17517,7 +17517,7 @@
         <v>4</v>
       </c>
       <c r="F735" s="5">
-        <v>0.05169019526382272</v>
+        <v>0.05465177331112318</v>
       </c>
       <c r="G735" s="6">
         <v>14</v>
@@ -17540,7 +17540,7 @@
         <v>5</v>
       </c>
       <c r="F736" s="5">
-        <v>0.05577142261318894</v>
+        <v>0.04947560920000061</v>
       </c>
       <c r="G736" s="6">
         <v>15</v>
@@ -17563,7 +17563,7 @@
         <v>1</v>
       </c>
       <c r="F737" s="5">
-        <v>-0.0006923655320501953</v>
+        <v>-0.004014227299165167</v>
       </c>
       <c r="G737" s="6">
         <v>14</v>
@@ -17586,7 +17586,7 @@
         <v>2</v>
       </c>
       <c r="F738" s="5">
-        <v>-0.006931983231301717</v>
+        <v>-0.009245446794630408</v>
       </c>
       <c r="G738" s="6">
         <v>14</v>
@@ -17609,7 +17609,7 @@
         <v>3</v>
       </c>
       <c r="F739" s="5">
-        <v>-0.001453684345678437</v>
+        <v>-0.003574971730161484</v>
       </c>
       <c r="G739" s="6">
         <v>15</v>
@@ -17632,7 +17632,7 @@
         <v>4</v>
       </c>
       <c r="F740" s="5">
-        <v>0.01102338030338124</v>
+        <v>0.01100768224877566</v>
       </c>
       <c r="G740" s="6">
         <v>14</v>
@@ -17655,7 +17655,7 @@
         <v>5</v>
       </c>
       <c r="F741" s="5">
-        <v>-0.006799510285875952</v>
+        <v>0.0005960655913197175</v>
       </c>
       <c r="G741" s="6">
         <v>15</v>
@@ -17678,7 +17678,7 @@
         <v>1</v>
       </c>
       <c r="F742" s="5">
-        <v>0.008437233367322819</v>
+        <v>0.007668385597403155</v>
       </c>
       <c r="G742" s="6">
         <v>14</v>
@@ -17701,7 +17701,7 @@
         <v>2</v>
       </c>
       <c r="F743" s="5">
-        <v>0.0003838663118567488</v>
+        <v>0.001660828619962956</v>
       </c>
       <c r="G743" s="6">
         <v>14</v>
@@ -17724,7 +17724,7 @@
         <v>3</v>
       </c>
       <c r="F744" s="5">
-        <v>-0.0110907387643451</v>
+        <v>-0.01689217461539752</v>
       </c>
       <c r="G744" s="6">
         <v>15</v>
@@ -17747,7 +17747,7 @@
         <v>4</v>
       </c>
       <c r="F745" s="5">
-        <v>-0.0007264190268548703</v>
+        <v>0.01479326209039979</v>
       </c>
       <c r="G745" s="6">
         <v>14</v>
@@ -17770,7 +17770,7 @@
         <v>5</v>
       </c>
       <c r="F746" s="5">
-        <v>0.02451251290236039</v>
+        <v>0.01535467280833435</v>
       </c>
       <c r="G746" s="6">
         <v>15</v>
@@ -17793,7 +17793,7 @@
         <v>1</v>
       </c>
       <c r="F747" s="5">
-        <v>-0.004828025483967568</v>
+        <v>-0.01290520586950456</v>
       </c>
       <c r="G747" s="6">
         <v>14</v>
@@ -17816,7 +17816,7 @@
         <v>2</v>
       </c>
       <c r="F748" s="5">
-        <v>0.006219608535954422</v>
+        <v>0.002761530029322289</v>
       </c>
       <c r="G748" s="6">
         <v>14</v>
@@ -17839,7 +17839,7 @@
         <v>3</v>
       </c>
       <c r="F749" s="5">
-        <v>-0.02032228301163981</v>
+        <v>-0.01143679630928908</v>
       </c>
       <c r="G749" s="6">
         <v>15</v>
@@ -17862,7 +17862,7 @@
         <v>4</v>
       </c>
       <c r="F750" s="5">
-        <v>0.0001709417876769169</v>
+        <v>0.008943657770825038</v>
       </c>
       <c r="G750" s="6">
         <v>14</v>
@@ -17885,7 +17885,7 @@
         <v>5</v>
       </c>
       <c r="F751" s="5">
-        <v>0.02414057744325686</v>
+        <v>0.01783346412265907</v>
       </c>
       <c r="G751" s="6">
         <v>15</v>
@@ -17908,7 +17908,7 @@
         <v>1</v>
       </c>
       <c r="F752" s="5">
-        <v>-0.01471788150730867</v>
+        <v>-0.0126922025600305</v>
       </c>
       <c r="G752" s="6">
         <v>14</v>
@@ -17931,7 +17931,7 @@
         <v>2</v>
       </c>
       <c r="F753" s="5">
-        <v>-0.01651151720942323</v>
+        <v>-0.02241626185009857</v>
       </c>
       <c r="G753" s="6">
         <v>14</v>
@@ -17954,7 +17954,7 @@
         <v>3</v>
       </c>
       <c r="F754" s="5">
-        <v>-0.01575646040592531</v>
+        <v>-0.02093750104989775</v>
       </c>
       <c r="G754" s="6">
         <v>15</v>
@@ -17977,7 +17977,7 @@
         <v>4</v>
       </c>
       <c r="F755" s="5">
-        <v>-0.02046588842782521</v>
+        <v>-0.008551513823826422</v>
       </c>
       <c r="G755" s="6">
         <v>14</v>
@@ -18000,7 +18000,7 @@
         <v>5</v>
       </c>
       <c r="F756" s="5">
-        <v>-0.01449489751872357</v>
+        <v>-0.01681347852464597</v>
       </c>
       <c r="G756" s="6">
         <v>15</v>
@@ -18023,7 +18023,7 @@
         <v>1</v>
       </c>
       <c r="F757" s="5">
-        <v>0.01323960805009612</v>
+        <v>0.008261382538941259</v>
       </c>
       <c r="G757" s="6">
         <v>14</v>
@@ -18046,7 +18046,7 @@
         <v>2</v>
       </c>
       <c r="F758" s="5">
-        <v>0.01736826595264926</v>
+        <v>0.01146877024609931</v>
       </c>
       <c r="G758" s="6">
         <v>14</v>
@@ -18069,7 +18069,7 @@
         <v>3</v>
       </c>
       <c r="F759" s="5">
-        <v>-0.002409706870097034</v>
+        <v>0.001204198607909899</v>
       </c>
       <c r="G759" s="6">
         <v>15</v>
@@ -18092,7 +18092,7 @@
         <v>4</v>
       </c>
       <c r="F760" s="5">
-        <v>0.01252689135819257</v>
+        <v>0.02520424496428375</v>
       </c>
       <c r="G760" s="6">
         <v>14</v>
@@ -18115,7 +18115,7 @@
         <v>5</v>
       </c>
       <c r="F761" s="5">
-        <v>0.01448192368320547</v>
+        <v>0.009188361309371264</v>
       </c>
       <c r="G761" s="6">
         <v>15</v>
@@ -18138,7 +18138,7 @@
         <v>1</v>
       </c>
       <c r="F762" s="5">
-        <v>-0.01426646199770902</v>
+        <v>-0.02038549457568094</v>
       </c>
       <c r="G762" s="6">
         <v>14</v>
@@ -18161,7 +18161,7 @@
         <v>2</v>
       </c>
       <c r="F763" s="5">
-        <v>-0.02125207508144297</v>
+        <v>-0.0008136346514180946</v>
       </c>
       <c r="G763" s="6">
         <v>14</v>
@@ -18184,7 +18184,7 @@
         <v>3</v>
       </c>
       <c r="F764" s="5">
-        <v>0.005974246625382465</v>
+        <v>-0.002271071024402343</v>
       </c>
       <c r="G764" s="6">
         <v>15</v>
@@ -18207,7 +18207,7 @@
         <v>4</v>
       </c>
       <c r="F765" s="5">
-        <v>-0.004228097572978255</v>
+        <v>-0.005865447550508926</v>
       </c>
       <c r="G765" s="6">
         <v>14</v>
@@ -18230,7 +18230,7 @@
         <v>5</v>
       </c>
       <c r="F766" s="5">
-        <v>-0.00034638072450341</v>
+        <v>-0.003937650424272729</v>
       </c>
       <c r="G766" s="6">
         <v>15</v>
@@ -18253,7 +18253,7 @@
         <v>1</v>
       </c>
       <c r="F767" s="5">
-        <v>-0.001861139513109388</v>
+        <v>-0.008829561615813211</v>
       </c>
       <c r="G767" s="6">
         <v>14</v>
@@ -18276,7 +18276,7 @@
         <v>2</v>
       </c>
       <c r="F768" s="5">
-        <v>-0.00509530274764482</v>
+        <v>0.002500929265483968</v>
       </c>
       <c r="G768" s="6">
         <v>14</v>
@@ -18299,7 +18299,7 @@
         <v>3</v>
       </c>
       <c r="F769" s="5">
-        <v>-0.003696179663573869</v>
+        <v>-0.0104152033566991</v>
       </c>
       <c r="G769" s="6">
         <v>15</v>
@@ -18322,7 +18322,7 @@
         <v>4</v>
       </c>
       <c r="F770" s="5">
-        <v>-0.01191946564189626</v>
+        <v>-0.01076086784210673</v>
       </c>
       <c r="G770" s="6">
         <v>14</v>
@@ -18345,7 +18345,7 @@
         <v>5</v>
       </c>
       <c r="F771" s="5">
-        <v>0.00485817564157274</v>
+        <v>0.009909885471831102</v>
       </c>
       <c r="G771" s="6">
         <v>15</v>
@@ -18368,7 +18368,7 @@
         <v>1</v>
       </c>
       <c r="F772" s="5">
-        <v>-0.03378893957465494</v>
+        <v>-0.02041787659477016</v>
       </c>
       <c r="G772" s="6">
         <v>14</v>
@@ -18391,7 +18391,7 @@
         <v>2</v>
       </c>
       <c r="F773" s="5">
-        <v>-0.008113598330256796</v>
+        <v>-0.03407460051949117</v>
       </c>
       <c r="G773" s="6">
         <v>14</v>
@@ -18414,7 +18414,7 @@
         <v>3</v>
       </c>
       <c r="F774" s="5">
-        <v>-0.01283194539302826</v>
+        <v>-0.01213387637724547</v>
       </c>
       <c r="G774" s="6">
         <v>15</v>
@@ -18437,7 +18437,7 @@
         <v>4</v>
       </c>
       <c r="F775" s="5">
-        <v>-0.01429728511198243</v>
+        <v>-0.004610440676541239</v>
       </c>
       <c r="G775" s="6">
         <v>14</v>
@@ -18460,7 +18460,7 @@
         <v>5</v>
       </c>
       <c r="F776" s="5">
-        <v>-0.009116709489909702</v>
+        <v>-0.007105223383377973</v>
       </c>
       <c r="G776" s="6">
         <v>15</v>
@@ -18483,7 +18483,7 @@
         <v>1</v>
       </c>
       <c r="F777" s="5">
-        <v>-0.01701740481522478</v>
+        <v>-0.02321725266489736</v>
       </c>
       <c r="G777" s="6">
         <v>14</v>
@@ -18506,7 +18506,7 @@
         <v>2</v>
       </c>
       <c r="F778" s="5">
-        <v>-0.02218138261043832</v>
+        <v>-0.02991497103461211</v>
       </c>
       <c r="G778" s="6">
         <v>14</v>
@@ -18529,7 +18529,7 @@
         <v>3</v>
       </c>
       <c r="F779" s="5">
-        <v>-0.03979989357259107</v>
+        <v>-0.02303824714204604</v>
       </c>
       <c r="G779" s="6">
         <v>15</v>
@@ -18552,7 +18552,7 @@
         <v>4</v>
       </c>
       <c r="F780" s="5">
-        <v>-0.03892082696563594</v>
+        <v>-0.04602158754615352</v>
       </c>
       <c r="G780" s="6">
         <v>14</v>
@@ -18575,7 +18575,7 @@
         <v>5</v>
       </c>
       <c r="F781" s="5">
-        <v>-0.02631080376109236</v>
+        <v>-0.02344053312756439</v>
       </c>
       <c r="G781" s="6">
         <v>15</v>
@@ -18598,7 +18598,7 @@
         <v>1</v>
       </c>
       <c r="F782" s="5">
-        <v>0.01073226331269732</v>
+        <v>-0.000795370870679767</v>
       </c>
       <c r="G782" s="6">
         <v>14</v>
@@ -18621,7 +18621,7 @@
         <v>2</v>
       </c>
       <c r="F783" s="5">
-        <v>0.01390222418757928</v>
+        <v>0.02732239474266201</v>
       </c>
       <c r="G783" s="6">
         <v>14</v>
@@ -18644,7 +18644,7 @@
         <v>3</v>
       </c>
       <c r="F784" s="5">
-        <v>-0.009945274944643893</v>
+        <v>0.02499097153705037</v>
       </c>
       <c r="G784" s="6">
         <v>15</v>
@@ -18667,7 +18667,7 @@
         <v>4</v>
       </c>
       <c r="F785" s="5">
-        <v>0.0008945380331273582</v>
+        <v>-0.02639456908797532</v>
       </c>
       <c r="G785" s="6">
         <v>14</v>
@@ -18690,7 +18690,7 @@
         <v>5</v>
       </c>
       <c r="F786" s="5">
-        <v>0.01761308733698556</v>
+        <v>0.006380306888061861</v>
       </c>
       <c r="G786" s="6">
         <v>15</v>
@@ -18713,7 +18713,7 @@
         <v>1</v>
       </c>
       <c r="F787" s="5">
-        <v>-0.04609202615534878</v>
+        <v>-0.02872888699292137</v>
       </c>
       <c r="G787" s="6">
         <v>14</v>
@@ -18736,7 +18736,7 @@
         <v>2</v>
       </c>
       <c r="F788" s="5">
-        <v>-0.008606041996626597</v>
+        <v>-0.03051068433977096</v>
       </c>
       <c r="G788" s="6">
         <v>14</v>
@@ -18759,7 +18759,7 @@
         <v>3</v>
       </c>
       <c r="F789" s="5">
-        <v>-0.03300047268300292</v>
+        <v>-0.04431010302734349</v>
       </c>
       <c r="G789" s="6">
         <v>15</v>
@@ -18782,7 +18782,7 @@
         <v>4</v>
       </c>
       <c r="F790" s="5">
-        <v>-0.03281937551616908</v>
+        <v>-0.02160757253615048</v>
       </c>
       <c r="G790" s="6">
         <v>14</v>
@@ -18805,7 +18805,7 @@
         <v>5</v>
       </c>
       <c r="F791" s="5">
-        <v>-0.03931141432781873</v>
+        <v>-0.03422739712949305</v>
       </c>
       <c r="G791" s="6">
         <v>15</v>
@@ -18828,7 +18828,7 @@
         <v>1</v>
       </c>
       <c r="F792" s="5">
-        <v>0.02178691134461181</v>
+        <v>0.013446357477457</v>
       </c>
       <c r="G792" s="6">
         <v>14</v>
@@ -18851,7 +18851,7 @@
         <v>2</v>
       </c>
       <c r="F793" s="5">
-        <v>0.001250429171959178</v>
+        <v>0.005505889307955679</v>
       </c>
       <c r="G793" s="6">
         <v>14</v>
@@ -18874,7 +18874,7 @@
         <v>3</v>
       </c>
       <c r="F794" s="5">
-        <v>0.007455495442120364</v>
+        <v>0.01633277973974302</v>
       </c>
       <c r="G794" s="6">
         <v>15</v>
@@ -18897,7 +18897,7 @@
         <v>4</v>
       </c>
       <c r="F795" s="5">
-        <v>0.02679920353070065</v>
+        <v>0.02168780235438687</v>
       </c>
       <c r="G795" s="6">
         <v>14</v>
@@ -18920,7 +18920,7 @@
         <v>5</v>
       </c>
       <c r="F796" s="5">
-        <v>0.007122875388403473</v>
+        <v>0.006828986337754764</v>
       </c>
       <c r="G796" s="6">
         <v>15</v>
@@ -18943,7 +18943,7 @@
         <v>1</v>
       </c>
       <c r="F797" s="5">
-        <v>-0.01203969865172918</v>
+        <v>-0.01540661390839984</v>
       </c>
       <c r="G797" s="6">
         <v>14</v>
@@ -18966,7 +18966,7 @@
         <v>2</v>
       </c>
       <c r="F798" s="5">
-        <v>-0.001500565722797921</v>
+        <v>-0.008043711179214761</v>
       </c>
       <c r="G798" s="6">
         <v>14</v>
@@ -18989,7 +18989,7 @@
         <v>3</v>
       </c>
       <c r="F799" s="5">
-        <v>0.0006314849497969659</v>
+        <v>-0.007833272192320865</v>
       </c>
       <c r="G799" s="6">
         <v>15</v>
@@ -19012,7 +19012,7 @@
         <v>4</v>
       </c>
       <c r="F800" s="5">
-        <v>-0.005561728763369618</v>
+        <v>0.001468701101858154</v>
       </c>
       <c r="G800" s="6">
         <v>14</v>
@@ -19035,7 +19035,7 @@
         <v>5</v>
       </c>
       <c r="F801" s="5">
-        <v>-0.00409859299039747</v>
+        <v>0.007053819609722773</v>
       </c>
       <c r="G801" s="6">
         <v>15</v>
@@ -19058,7 +19058,7 @@
         <v>1</v>
       </c>
       <c r="F802" s="5">
-        <v>0.02120257607802276</v>
+        <v>0.006367797504881628</v>
       </c>
       <c r="G802" s="6">
         <v>14</v>
@@ -19081,7 +19081,7 @@
         <v>2</v>
       </c>
       <c r="F803" s="5">
-        <v>-0.0009991610329605544</v>
+        <v>0.0001830054763492398</v>
       </c>
       <c r="G803" s="6">
         <v>14</v>
@@ -19104,7 +19104,7 @@
         <v>3</v>
       </c>
       <c r="F804" s="5">
-        <v>0.01077017649672172</v>
+        <v>0.03662576601256981</v>
       </c>
       <c r="G804" s="6">
         <v>15</v>
@@ -19127,7 +19127,7 @@
         <v>4</v>
       </c>
       <c r="F805" s="5">
-        <v>0.03336908441115179</v>
+        <v>0.0102373533137753</v>
       </c>
       <c r="G805" s="6">
         <v>14</v>
@@ -19150,7 +19150,7 @@
         <v>5</v>
       </c>
       <c r="F806" s="5">
-        <v>-0.007079075067114646</v>
+        <v>0.001397389034164583</v>
       </c>
       <c r="G806" s="6">
         <v>15</v>
@@ -19173,7 +19173,7 @@
         <v>1</v>
       </c>
       <c r="F807" s="5">
-        <v>0.002991123082016141</v>
+        <v>0.006531263834735806</v>
       </c>
       <c r="G807" s="6">
         <v>14</v>
@@ -19196,7 +19196,7 @@
         <v>2</v>
       </c>
       <c r="F808" s="5">
-        <v>0.002385993529226867</v>
+        <v>-0.0005119386597940373</v>
       </c>
       <c r="G808" s="6">
         <v>14</v>
@@ -19219,7 +19219,7 @@
         <v>3</v>
       </c>
       <c r="F809" s="5">
-        <v>-0.01792265543711212</v>
+        <v>-0.02736014732650578</v>
       </c>
       <c r="G809" s="6">
         <v>15</v>
@@ -19242,7 +19242,7 @@
         <v>4</v>
       </c>
       <c r="F810" s="5">
-        <v>-0.01274138287375478</v>
+        <v>-0.009963976536946403</v>
       </c>
       <c r="G810" s="6">
         <v>14</v>
@@ -19265,7 +19265,7 @@
         <v>5</v>
       </c>
       <c r="F811" s="5">
-        <v>-0.002232619267499699</v>
+        <v>0.004013232048087302</v>
       </c>
       <c r="G811" s="6">
         <v>15</v>
@@ -19288,7 +19288,7 @@
         <v>1</v>
       </c>
       <c r="F812" s="5">
-        <v>-0.01969320750763645</v>
+        <v>-0.001068528501853588</v>
       </c>
       <c r="G812" s="6">
         <v>14</v>
@@ -19311,7 +19311,7 @@
         <v>2</v>
       </c>
       <c r="F813" s="5">
-        <v>-0.001875241024387702</v>
+        <v>-0.01388925932953745</v>
       </c>
       <c r="G813" s="6">
         <v>14</v>
@@ -19334,7 +19334,7 @@
         <v>3</v>
       </c>
       <c r="F814" s="5">
-        <v>0.02390208664401471</v>
+        <v>0.02997795958175571</v>
       </c>
       <c r="G814" s="6">
         <v>15</v>
@@ -19357,7 +19357,7 @@
         <v>4</v>
       </c>
       <c r="F815" s="5">
-        <v>0.01465672412425092</v>
+        <v>-0.003993042939058043</v>
       </c>
       <c r="G815" s="6">
         <v>14</v>
@@ -19380,7 +19380,7 @@
         <v>5</v>
       </c>
       <c r="F816" s="5">
-        <v>0.009447758874778563</v>
+        <v>0.01460838520886835</v>
       </c>
       <c r="G816" s="6">
         <v>15</v>
@@ -19403,7 +19403,7 @@
         <v>1</v>
       </c>
       <c r="F817" s="5">
-        <v>-0.01078309843396509</v>
+        <v>0.001657155579506821</v>
       </c>
       <c r="G817" s="6">
         <v>14</v>
@@ -19426,7 +19426,7 @@
         <v>2</v>
       </c>
       <c r="F818" s="5">
-        <v>0.02619292327608902</v>
+        <v>-0.02342775708380468</v>
       </c>
       <c r="G818" s="6">
         <v>14</v>
@@ -19449,7 +19449,7 @@
         <v>3</v>
       </c>
       <c r="F819" s="5">
-        <v>-0.02322441464469126</v>
+        <v>0.005816397182500308</v>
       </c>
       <c r="G819" s="6">
         <v>15</v>
@@ -19472,7 +19472,7 @@
         <v>4</v>
       </c>
       <c r="F820" s="5">
-        <v>0.01103895165067502</v>
+        <v>-0.009915234676646012</v>
       </c>
       <c r="G820" s="6">
         <v>14</v>
@@ -19495,7 +19495,7 @@
         <v>5</v>
       </c>
       <c r="F821" s="5">
-        <v>-0.00884702471643763</v>
+        <v>0.01637113528519744</v>
       </c>
       <c r="G821" s="6">
         <v>15</v>
@@ -19518,7 +19518,7 @@
         <v>1</v>
       </c>
       <c r="F822" s="5">
-        <v>-0.001243063372538464</v>
+        <v>0.008173143385186968</v>
       </c>
       <c r="G822" s="6">
         <v>14</v>
@@ -19541,7 +19541,7 @@
         <v>2</v>
       </c>
       <c r="F823" s="5">
-        <v>0.02903641859230591</v>
+        <v>0.01934853155436105</v>
       </c>
       <c r="G823" s="6">
         <v>14</v>
@@ -19564,7 +19564,7 @@
         <v>3</v>
       </c>
       <c r="F824" s="5">
-        <v>0.01971972653725887</v>
+        <v>0.0230459763976775</v>
       </c>
       <c r="G824" s="6">
         <v>15</v>
@@ -19587,7 +19587,7 @@
         <v>4</v>
       </c>
       <c r="F825" s="5">
-        <v>0.0130731917298084</v>
+        <v>0.02205632412669123</v>
       </c>
       <c r="G825" s="6">
         <v>14</v>
@@ -19610,7 +19610,7 @@
         <v>5</v>
       </c>
       <c r="F826" s="5">
-        <v>0.02574248547327427</v>
+        <v>0.01428554697063646</v>
       </c>
       <c r="G826" s="6">
         <v>15</v>
@@ -19633,7 +19633,7 @@
         <v>1</v>
       </c>
       <c r="F827" s="5">
-        <v>-0.003663868188235151</v>
+        <v>-0.01137187326751899</v>
       </c>
       <c r="G827" s="6">
         <v>14</v>
@@ -19656,7 +19656,7 @@
         <v>2</v>
       </c>
       <c r="F828" s="5">
-        <v>-0.006380154868255421</v>
+        <v>0.004471596622448328</v>
       </c>
       <c r="G828" s="6">
         <v>14</v>
@@ -19679,7 +19679,7 @@
         <v>3</v>
       </c>
       <c r="F829" s="5">
-        <v>-0.01646292686889003</v>
+        <v>-4.733026554305519E-05</v>
       </c>
       <c r="G829" s="6">
         <v>15</v>
@@ -19702,7 +19702,7 @@
         <v>4</v>
       </c>
       <c r="F830" s="5">
-        <v>-0.007455062945272579</v>
+        <v>-0.01244206649542261</v>
       </c>
       <c r="G830" s="6">
         <v>14</v>
@@ -19725,7 +19725,7 @@
         <v>5</v>
       </c>
       <c r="F831" s="5">
-        <v>-0.008401486048657236</v>
+        <v>-0.02309670932252277</v>
       </c>
       <c r="G831" s="6">
         <v>15</v>
@@ -19748,7 +19748,7 @@
         <v>1</v>
       </c>
       <c r="F832" s="5">
-        <v>-0.004394470747726617</v>
+        <v>0.003543221051246241</v>
       </c>
       <c r="G832" s="6">
         <v>14</v>
@@ -19771,7 +19771,7 @@
         <v>2</v>
       </c>
       <c r="F833" s="5">
-        <v>0.02498309210361339</v>
+        <v>0.01098458563238979</v>
       </c>
       <c r="G833" s="6">
         <v>14</v>
@@ -19794,7 +19794,7 @@
         <v>3</v>
       </c>
       <c r="F834" s="5">
-        <v>0.02155259709186288</v>
+        <v>0.03490993953662999</v>
       </c>
       <c r="G834" s="6">
         <v>15</v>
@@ -19817,7 +19817,7 @@
         <v>4</v>
       </c>
       <c r="F835" s="5">
-        <v>0.007614325086422753</v>
+        <v>0.02029960709997456</v>
       </c>
       <c r="G835" s="6">
         <v>14</v>
@@ -19840,7 +19840,7 @@
         <v>5</v>
       </c>
       <c r="F836" s="5">
-        <v>0.008668412638395843</v>
+        <v>-0.01087176599158558</v>
       </c>
       <c r="G836" s="6">
         <v>15</v>
@@ -19863,7 +19863,7 @@
         <v>1</v>
       </c>
       <c r="F837" s="5">
-        <v>-0.004963339791493141</v>
+        <v>0.009912039292718647</v>
       </c>
       <c r="G837" s="6">
         <v>14</v>
@@ -19886,7 +19886,7 @@
         <v>2</v>
       </c>
       <c r="F838" s="5">
-        <v>0.005234744198294329</v>
+        <v>-0.003231177928620661</v>
       </c>
       <c r="G838" s="6">
         <v>14</v>
@@ -19909,7 +19909,7 @@
         <v>3</v>
       </c>
       <c r="F839" s="5">
-        <v>0.01684342348538682</v>
+        <v>0.003921264075707489</v>
       </c>
       <c r="G839" s="6">
         <v>15</v>
@@ -19932,7 +19932,7 @@
         <v>4</v>
       </c>
       <c r="F840" s="5">
-        <v>0.01706633740534474</v>
+        <v>0.02422425574684022</v>
       </c>
       <c r="G840" s="6">
         <v>14</v>
@@ -19955,7 +19955,7 @@
         <v>5</v>
       </c>
       <c r="F841" s="5">
-        <v>-0.004978030280254389</v>
+        <v>-0.004718754482781184</v>
       </c>
       <c r="G841" s="6">
         <v>15</v>
@@ -19978,7 +19978,7 @@
         <v>1</v>
       </c>
       <c r="F842" s="5">
-        <v>0.03000065287461495</v>
+        <v>0.03638192249160061</v>
       </c>
       <c r="G842" s="6">
         <v>14</v>
@@ -20001,7 +20001,7 @@
         <v>2</v>
       </c>
       <c r="F843" s="5">
-        <v>0.03871631756595743</v>
+        <v>0.01461283789472608</v>
       </c>
       <c r="G843" s="6">
         <v>14</v>
@@ -20024,7 +20024,7 @@
         <v>3</v>
       </c>
       <c r="F844" s="5">
-        <v>0.02294986614948542</v>
+        <v>0.04446663273668251</v>
       </c>
       <c r="G844" s="6">
         <v>15</v>
@@ -20047,7 +20047,7 @@
         <v>4</v>
       </c>
       <c r="F845" s="5">
-        <v>0.03681913902868842</v>
+        <v>0.03825191872899331</v>
       </c>
       <c r="G845" s="6">
         <v>14</v>
@@ -20070,7 +20070,7 @@
         <v>5</v>
       </c>
       <c r="F846" s="5">
-        <v>0.03213423869507407</v>
+        <v>0.02582094043822173</v>
       </c>
       <c r="G846" s="6">
         <v>15</v>
@@ -20093,7 +20093,7 @@
         <v>1</v>
       </c>
       <c r="F847" s="5">
-        <v>0.04440124061767146</v>
+        <v>0.04519887262324324</v>
       </c>
       <c r="G847" s="6">
         <v>14</v>
@@ -20116,7 +20116,7 @@
         <v>2</v>
       </c>
       <c r="F848" s="5">
-        <v>0.02752609621927387</v>
+        <v>0.03767476948918885</v>
       </c>
       <c r="G848" s="6">
         <v>14</v>
@@ -20139,7 +20139,7 @@
         <v>3</v>
       </c>
       <c r="F849" s="5">
-        <v>0.04536357280447883</v>
+        <v>0.03358911428113224</v>
       </c>
       <c r="G849" s="6">
         <v>15</v>
@@ -20162,7 +20162,7 @@
         <v>4</v>
       </c>
       <c r="F850" s="5">
-        <v>0.05184012189535674</v>
+        <v>0.05504117371722232</v>
       </c>
       <c r="G850" s="6">
         <v>14</v>
@@ -20185,7 +20185,7 @@
         <v>5</v>
       </c>
       <c r="F851" s="5">
-        <v>0.05944761294321912</v>
+        <v>0.05801787150903686</v>
       </c>
       <c r="G851" s="6">
         <v>15</v>
@@ -20208,7 +20208,7 @@
         <v>1</v>
       </c>
       <c r="F852" s="5">
-        <v>-0.008728409117176036</v>
+        <v>-0.00483530793313918</v>
       </c>
       <c r="G852" s="6">
         <v>14</v>
@@ -20231,7 +20231,7 @@
         <v>2</v>
       </c>
       <c r="F853" s="5">
-        <v>0.001388286425934117</v>
+        <v>-0.001112746715733826</v>
       </c>
       <c r="G853" s="6">
         <v>14</v>
@@ -20254,7 +20254,7 @@
         <v>3</v>
       </c>
       <c r="F854" s="5">
-        <v>0.000723217866296109</v>
+        <v>-0.005521928192092427</v>
       </c>
       <c r="G854" s="6">
         <v>15</v>
@@ -20277,7 +20277,7 @@
         <v>4</v>
       </c>
       <c r="F855" s="5">
-        <v>0.004310197954136599</v>
+        <v>0.01296130849215536</v>
       </c>
       <c r="G855" s="6">
         <v>14</v>
@@ -20300,7 +20300,7 @@
         <v>5</v>
       </c>
       <c r="F856" s="5">
-        <v>-0.00297605330585816</v>
+        <v>-0.006104540589164787</v>
       </c>
       <c r="G856" s="6">
         <v>15</v>
@@ -20323,7 +20323,7 @@
         <v>1</v>
       </c>
       <c r="F857" s="5">
-        <v>0.006389222544242862</v>
+        <v>0.01371764832937762</v>
       </c>
       <c r="G857" s="6">
         <v>14</v>
@@ -20346,7 +20346,7 @@
         <v>2</v>
       </c>
       <c r="F858" s="5">
-        <v>-0.001203165803789041</v>
+        <v>-0.005864605847840099</v>
       </c>
       <c r="G858" s="6">
         <v>14</v>
@@ -20369,7 +20369,7 @@
         <v>3</v>
       </c>
       <c r="F859" s="5">
-        <v>-0.01388189394854821</v>
+        <v>-0.006531726368261173</v>
       </c>
       <c r="G859" s="6">
         <v>15</v>
@@ -20392,7 +20392,7 @@
         <v>4</v>
       </c>
       <c r="F860" s="5">
-        <v>0.0008554220307992763</v>
+        <v>0.001969131116848764</v>
       </c>
       <c r="G860" s="6">
         <v>14</v>
@@ -20415,7 +20415,7 @@
         <v>5</v>
       </c>
       <c r="F861" s="5">
-        <v>0.02921998984223033</v>
+        <v>0.01834117375661897</v>
       </c>
       <c r="G861" s="6">
         <v>15</v>
@@ -20438,7 +20438,7 @@
         <v>1</v>
       </c>
       <c r="F862" s="5">
-        <v>-0.01589433371149945</v>
+        <v>-0.0125952437439432</v>
       </c>
       <c r="G862" s="6">
         <v>14</v>
@@ -20461,7 +20461,7 @@
         <v>2</v>
       </c>
       <c r="F863" s="5">
-        <v>0.01323400473767885</v>
+        <v>-0.004287971799148608</v>
       </c>
       <c r="G863" s="6">
         <v>14</v>
@@ -20484,7 +20484,7 @@
         <v>3</v>
       </c>
       <c r="F864" s="5">
-        <v>-0.009108878159270559</v>
+        <v>0.003665995458583044</v>
       </c>
       <c r="G864" s="6">
         <v>15</v>
@@ -20507,7 +20507,7 @@
         <v>4</v>
       </c>
       <c r="F865" s="5">
-        <v>-0.003992330986594996</v>
+        <v>0.008138682343549069</v>
       </c>
       <c r="G865" s="6">
         <v>14</v>
@@ -20530,7 +20530,7 @@
         <v>5</v>
       </c>
       <c r="F866" s="5">
-        <v>0.02059467840429502</v>
+        <v>0.009772219809626751</v>
       </c>
       <c r="G866" s="6">
         <v>15</v>
@@ -20553,7 +20553,7 @@
         <v>1</v>
       </c>
       <c r="F867" s="5">
-        <v>-0.008958483539669921</v>
+        <v>-0.01008052451211664</v>
       </c>
       <c r="G867" s="6">
         <v>14</v>
@@ -20576,7 +20576,7 @@
         <v>2</v>
       </c>
       <c r="F868" s="5">
-        <v>-0.02054768463872957</v>
+        <v>-0.02786124696163535</v>
       </c>
       <c r="G868" s="6">
         <v>14</v>
@@ -20599,7 +20599,7 @@
         <v>3</v>
       </c>
       <c r="F869" s="5">
-        <v>-0.01173474545861637</v>
+        <v>-0.01393351047303244</v>
       </c>
       <c r="G869" s="6">
         <v>15</v>
@@ -20622,7 +20622,7 @@
         <v>4</v>
       </c>
       <c r="F870" s="5">
-        <v>-0.02343602687095674</v>
+        <v>-0.01262663315719904</v>
       </c>
       <c r="G870" s="6">
         <v>14</v>
@@ -20645,7 +20645,7 @@
         <v>5</v>
       </c>
       <c r="F871" s="5">
-        <v>-0.01735283175488666</v>
+        <v>-0.01736960446431545</v>
       </c>
       <c r="G871" s="6">
         <v>15</v>
@@ -20668,7 +20668,7 @@
         <v>1</v>
       </c>
       <c r="F872" s="5">
-        <v>0.02657043059831708</v>
+        <v>0.02024550399819532</v>
       </c>
       <c r="G872" s="6">
         <v>14</v>
@@ -20691,7 +20691,7 @@
         <v>2</v>
       </c>
       <c r="F873" s="5">
-        <v>0.008612561787188501</v>
+        <v>0.01116395835553564</v>
       </c>
       <c r="G873" s="6">
         <v>14</v>
@@ -20714,7 +20714,7 @@
         <v>3</v>
       </c>
       <c r="F874" s="5">
-        <v>-0.006797288638646415</v>
+        <v>0.001319548468451403</v>
       </c>
       <c r="G874" s="6">
         <v>15</v>
@@ -20737,7 +20737,7 @@
         <v>4</v>
       </c>
       <c r="F875" s="5">
-        <v>0.01308655367554824</v>
+        <v>0.0345188312238962</v>
       </c>
       <c r="G875" s="6">
         <v>14</v>
@@ -20760,7 +20760,7 @@
         <v>5</v>
       </c>
       <c r="F876" s="5">
-        <v>0.01407704346498004</v>
+        <v>-0.0105212913242529</v>
       </c>
       <c r="G876" s="6">
         <v>15</v>
@@ -20783,7 +20783,7 @@
         <v>1</v>
       </c>
       <c r="F877" s="5">
-        <v>-0.01788429237896856</v>
+        <v>-0.01059580591974121</v>
       </c>
       <c r="G877" s="6">
         <v>14</v>
@@ -20806,7 +20806,7 @@
         <v>2</v>
       </c>
       <c r="F878" s="5">
-        <v>0.0009130350193590853</v>
+        <v>-0.01684655764919092</v>
       </c>
       <c r="G878" s="6">
         <v>14</v>
@@ -20829,7 +20829,7 @@
         <v>3</v>
       </c>
       <c r="F879" s="5">
-        <v>-0.01076911177090772</v>
+        <v>-0.01058718382237967</v>
       </c>
       <c r="G879" s="6">
         <v>15</v>
@@ -20852,7 +20852,7 @@
         <v>4</v>
       </c>
       <c r="F880" s="5">
-        <v>-0.0147547682876877</v>
+        <v>0.01296665215979889</v>
       </c>
       <c r="G880" s="6">
         <v>14</v>
@@ -20875,7 +20875,7 @@
         <v>5</v>
       </c>
       <c r="F881" s="5">
-        <v>0.008911075933942574</v>
+        <v>-0.007371145303538477</v>
       </c>
       <c r="G881" s="6">
         <v>15</v>
@@ -20898,7 +20898,7 @@
         <v>1</v>
       </c>
       <c r="F882" s="5">
-        <v>-0.006903937743061263</v>
+        <v>-0.001931917713198389</v>
       </c>
       <c r="G882" s="6">
         <v>14</v>
@@ -20921,7 +20921,7 @@
         <v>2</v>
       </c>
       <c r="F883" s="5">
-        <v>-0.002920968841150417</v>
+        <v>-0.02403037701836324</v>
       </c>
       <c r="G883" s="6">
         <v>14</v>
@@ -20944,7 +20944,7 @@
         <v>3</v>
       </c>
       <c r="F884" s="5">
-        <v>-0.002120733096912532</v>
+        <v>0.008499503486395344</v>
       </c>
       <c r="G884" s="6">
         <v>15</v>
@@ -20967,7 +20967,7 @@
         <v>4</v>
       </c>
       <c r="F885" s="5">
-        <v>-0.004377278716543409</v>
+        <v>0.0001242830963276045</v>
       </c>
       <c r="G885" s="6">
         <v>14</v>
@@ -20990,7 +20990,7 @@
         <v>5</v>
       </c>
       <c r="F886" s="5">
-        <v>-0.001079412020190949</v>
+        <v>-0.0008395440246518217</v>
       </c>
       <c r="G886" s="6">
         <v>15</v>
@@ -21013,7 +21013,7 @@
         <v>1</v>
       </c>
       <c r="F887" s="5">
-        <v>-0.03395899311389639</v>
+        <v>-0.01940366231365234</v>
       </c>
       <c r="G887" s="6">
         <v>14</v>
@@ -21036,7 +21036,7 @@
         <v>2</v>
       </c>
       <c r="F888" s="5">
-        <v>-0.007862409898261046</v>
+        <v>-0.02017267071258726</v>
       </c>
       <c r="G888" s="6">
         <v>14</v>
@@ -21059,7 +21059,7 @@
         <v>3</v>
       </c>
       <c r="F889" s="5">
-        <v>-0.000824075251380473</v>
+        <v>-0.02694882403385548</v>
       </c>
       <c r="G889" s="6">
         <v>15</v>
@@ -21082,7 +21082,7 @@
         <v>4</v>
       </c>
       <c r="F890" s="5">
-        <v>-0.013930230550397</v>
+        <v>-0.004977013685831968</v>
       </c>
       <c r="G890" s="6">
         <v>14</v>
@@ -21105,7 +21105,7 @@
         <v>5</v>
       </c>
       <c r="F891" s="5">
-        <v>-0.02154288978894124</v>
+        <v>-0.005869875400250228</v>
       </c>
       <c r="G891" s="6">
         <v>15</v>
@@ -21128,7 +21128,7 @@
         <v>1</v>
       </c>
       <c r="F892" s="5">
-        <v>-0.02933797689804865</v>
+        <v>-0.02573382561590415</v>
       </c>
       <c r="G892" s="6">
         <v>14</v>
@@ -21151,7 +21151,7 @@
         <v>2</v>
       </c>
       <c r="F893" s="5">
-        <v>-0.02432860552295733</v>
+        <v>-0.04098889467639556</v>
       </c>
       <c r="G893" s="6">
         <v>14</v>
@@ -21174,7 +21174,7 @@
         <v>3</v>
       </c>
       <c r="F894" s="5">
-        <v>-0.03370186372609027</v>
+        <v>-0.00903297779046499</v>
       </c>
       <c r="G894" s="6">
         <v>15</v>
@@ -21197,7 +21197,7 @@
         <v>4</v>
       </c>
       <c r="F895" s="5">
-        <v>-0.04091184689485632</v>
+        <v>-0.06199183643346472</v>
       </c>
       <c r="G895" s="6">
         <v>14</v>
@@ -21220,7 +21220,7 @@
         <v>5</v>
       </c>
       <c r="F896" s="5">
-        <v>-0.01704727301133413</v>
+        <v>-0.009855773364384075</v>
       </c>
       <c r="G896" s="6">
         <v>15</v>
@@ -21243,7 +21243,7 @@
         <v>1</v>
       </c>
       <c r="F897" s="5">
-        <v>-0.002746741352071588</v>
+        <v>0.004709541186902742</v>
       </c>
       <c r="G897" s="6">
         <v>14</v>
@@ -21266,7 +21266,7 @@
         <v>2</v>
       </c>
       <c r="F898" s="5">
-        <v>0.02895309687698424</v>
+        <v>0.008325537761340512</v>
       </c>
       <c r="G898" s="6">
         <v>14</v>
@@ -21289,7 +21289,7 @@
         <v>3</v>
       </c>
       <c r="F899" s="5">
-        <v>-0.002221740151752104</v>
+        <v>-0.001536592204714582</v>
       </c>
       <c r="G899" s="6">
         <v>15</v>
@@ -21312,7 +21312,7 @@
         <v>4</v>
       </c>
       <c r="F900" s="5">
-        <v>-0.02153016667098994</v>
+        <v>0.03145377299549606</v>
       </c>
       <c r="G900" s="6">
         <v>14</v>
@@ -21335,7 +21335,7 @@
         <v>5</v>
       </c>
       <c r="F901" s="5">
-        <v>0.02935220011160959</v>
+        <v>-0.00849143338592342</v>
       </c>
       <c r="G901" s="6">
         <v>15</v>
@@ -21358,7 +21358,7 @@
         <v>1</v>
       </c>
       <c r="F902" s="5">
-        <v>-0.03008123346170249</v>
+        <v>-0.02055310436885905</v>
       </c>
       <c r="G902" s="6">
         <v>14</v>
@@ -21381,7 +21381,7 @@
         <v>2</v>
       </c>
       <c r="F903" s="5">
-        <v>-0.0333266756927291</v>
+        <v>-0.04883598798350771</v>
       </c>
       <c r="G903" s="6">
         <v>14</v>
@@ -21404,7 +21404,7 @@
         <v>3</v>
       </c>
       <c r="F904" s="5">
-        <v>-0.03684032673882284</v>
+        <v>-0.03285992765937444</v>
       </c>
       <c r="G904" s="6">
         <v>15</v>
@@ -21427,7 +21427,7 @@
         <v>4</v>
       </c>
       <c r="F905" s="5">
-        <v>-0.02847189587881534</v>
+        <v>-0.02937398132090171</v>
       </c>
       <c r="G905" s="6">
         <v>14</v>
@@ -21450,7 +21450,7 @@
         <v>5</v>
       </c>
       <c r="F906" s="5">
-        <v>-0.03140002299790319</v>
+        <v>-0.02895603801333147</v>
       </c>
       <c r="G906" s="6">
         <v>15</v>
@@ -21473,7 +21473,7 @@
         <v>1</v>
       </c>
       <c r="F907" s="5">
-        <v>0.00382621543809861</v>
+        <v>0.007547930115593133</v>
       </c>
       <c r="G907" s="6">
         <v>14</v>
@@ -21496,7 +21496,7 @@
         <v>2</v>
       </c>
       <c r="F908" s="5">
-        <v>0.01540074517262139</v>
+        <v>0.01089086587586436</v>
       </c>
       <c r="G908" s="6">
         <v>14</v>
@@ -21519,7 +21519,7 @@
         <v>3</v>
       </c>
       <c r="F909" s="5">
-        <v>0.01159013541398856</v>
+        <v>0.000426935498282061</v>
       </c>
       <c r="G909" s="6">
         <v>15</v>
@@ -21542,7 +21542,7 @@
         <v>4</v>
       </c>
       <c r="F910" s="5">
-        <v>0.002803635830403795</v>
+        <v>0.0260781661821608</v>
       </c>
       <c r="G910" s="6">
         <v>14</v>
@@ -21565,7 +21565,7 @@
         <v>5</v>
       </c>
       <c r="F911" s="5">
-        <v>0.02894045318227326</v>
+        <v>0.01911637841431823</v>
       </c>
       <c r="G911" s="6">
         <v>15</v>
@@ -21588,7 +21588,7 @@
         <v>1</v>
       </c>
       <c r="F912" s="5">
-        <v>-0.01071180581950086</v>
+        <v>-0.02297099287760226</v>
       </c>
       <c r="G912" s="6">
         <v>14</v>
@@ -21611,7 +21611,7 @@
         <v>2</v>
       </c>
       <c r="F913" s="5">
-        <v>0.002990175404332667</v>
+        <v>0.01064080788115043</v>
       </c>
       <c r="G913" s="6">
         <v>14</v>
@@ -21634,7 +21634,7 @@
         <v>3</v>
       </c>
       <c r="F914" s="5">
-        <v>-0.003974237608006161</v>
+        <v>-0.0006667550096548491</v>
       </c>
       <c r="G914" s="6">
         <v>15</v>
@@ -21657,7 +21657,7 @@
         <v>4</v>
       </c>
       <c r="F915" s="5">
-        <v>0.009289132123285235</v>
+        <v>-0.008422994964250039</v>
       </c>
       <c r="G915" s="6">
         <v>14</v>
@@ -21680,7 +21680,7 @@
         <v>5</v>
       </c>
       <c r="F916" s="5">
-        <v>-0.01878439895554052</v>
+        <v>-0.001259245329660846</v>
       </c>
       <c r="G916" s="6">
         <v>15</v>
@@ -21703,7 +21703,7 @@
         <v>1</v>
       </c>
       <c r="F917" s="5">
-        <v>0.001967369502423375</v>
+        <v>0.006131523732501609</v>
       </c>
       <c r="G917" s="6">
         <v>14</v>
@@ -21726,7 +21726,7 @@
         <v>2</v>
       </c>
       <c r="F918" s="5">
-        <v>0.009901483981451339</v>
+        <v>0.01063334086835546</v>
       </c>
       <c r="G918" s="6">
         <v>14</v>
@@ -21749,7 +21749,7 @@
         <v>3</v>
       </c>
       <c r="F919" s="5">
-        <v>0.006285872904598801</v>
+        <v>0.02089430826213445</v>
       </c>
       <c r="G919" s="6">
         <v>15</v>
@@ -21772,7 +21772,7 @@
         <v>4</v>
       </c>
       <c r="F920" s="5">
-        <v>0.03708463375279931</v>
+        <v>0.01689308443168055</v>
       </c>
       <c r="G920" s="6">
         <v>14</v>
@@ -21795,7 +21795,7 @@
         <v>5</v>
       </c>
       <c r="F921" s="5">
-        <v>0.001716306596578913</v>
+        <v>0.001383706896237246</v>
       </c>
       <c r="G921" s="6">
         <v>15</v>
